--- a/resources/data-imports/Monsters/surface-raid-monsters.xlsx
+++ b/resources/data-imports/Monsters/surface-raid-monsters.xlsx
@@ -406,34 +406,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -836,7 +836,7 @@
         <v>0.046079652675</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>348201663.24165</v>
+        <v>500000</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0.0571088175427612</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>410937957.07532</v>
+        <v>693267</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
         <v>0.0707778130216211</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>484977593.137006</v>
+        <v>961239</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0.0877184825683462</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>572357120.57101</v>
+        <v>1332790</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>0.10871390137108</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>675480018.260952</v>
+        <v>1847960</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0.134734573664248</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>797182805.404109</v>
+        <v>2562259</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0.166983293870785</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>940813063.379854</v>
+        <v>3552661</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>0</v>
@@ -1810,7 +1810,7 @@
         <v>0.206950745258758</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1110321514.99742</v>
+        <v>4925886</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>0.256484406136442</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1310370693.87335</v>
+        <v>6829909</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0.317873948745199</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>1546463193.02037</v>
+        <v>9469904</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>0.393957078377362</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>1825093020.27926</v>
+        <v>13130346</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>0.488250705086984</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>2153924223.80674</v>
+        <v>18205676</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>0.605113511349554</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>2542001700.92786</v>
+        <v>25242794</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
         <v>0.749947430291069</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>2999999988.90395</v>
+        <v>34999999</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>0</v>
